--- a/artfynd/A 22501-2025 artfynd.xlsx
+++ b/artfynd/A 22501-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150669</v>
+        <v>121150671</v>
       </c>
       <c r="B2" t="n">
-        <v>78344</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>439543</v>
+        <v>439544</v>
       </c>
       <c r="R2" t="n">
-        <v>6881094</v>
+        <v>6881093</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150671</v>
+        <v>121150669</v>
       </c>
       <c r="B3" t="n">
-        <v>78343</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>439544</v>
+        <v>439543</v>
       </c>
       <c r="R3" t="n">
-        <v>6881093</v>
+        <v>6881094</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
